--- a/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
+++ b/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="14 Alérgenos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Alérgenos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'14 Alérgenos'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -138,43 +140,43 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -534,15 +536,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -550,6 +553,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -557,9 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -581,13 +583,19 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -595,7 +603,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -604,15 +621,15 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="50"/>
-    <col customWidth="1" max="4" min="4" width="50"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,6 +646,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -931,6 +949,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="13" t="inlineStr">
         <is>
@@ -938,6 +957,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
@@ -957,7 +977,15 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
+++ b/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Alérgenos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'14 Alérgenos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'14 Alérgenos'!$A$1:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +91,39 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -115,8 +148,18 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -138,11 +181,69 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +273,39 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,16 +672,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Fichas de los 14 Alérgenos Obligatorios</t>
         </is>
@@ -555,7 +689,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -563,47 +697,111 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Imprime estas fichas y colócalas en cocina y sala</t>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>▸ Imprime las fichas y cuélgalas en la cocina y en la barra. Es un cartel de consulta, no un registro que se rellene.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Todo el personal debe conocer los 14 alérgenos</t>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>▸ Obligatorio según el Reglamento (UE) 1169/2011 y el RD 126/2015: la información sobre los 14 alérgenos tiene que estar a disposición del cliente, y el personal tiene que saber darla.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Obligatorio según Reglamento UE 1169/2011 (RD 126/2015 en España)</t>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>▸ La declaración plato a plato de TU carta va en el registro 08 (Matriz de alérgenos). Este cartel es la referencia común y el protocolo de actuación.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>El protocolo, en dos bloques</t>
         </is>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>▸ Antes de cocinar y al servir: seis pasos que evitan la contaminación cruzada, desde anotar la alergia en la comanda hasta entregar el plato en mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>▸ Si hay una reacción: cuatro pasos en orden de urgencia. El PRIMERO es llamar al 112, y el segundo la adrenalina autoinyectable si la persona la lleva; guardar el plato y la etiqueta va después. Se llama por síntomas —dificultad para respirar, hinchazón de labios o lengua, mareo, vómitos, urticaria extensa—, no por precaución.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>▸ Los dos bloques están pensados para leerse bajo presión: un paso por línea, numerados y sin letra pequeña.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Lo que más falla en la práctica</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>▸ La freidora y el agua de cocción compartidas. Un rebozado con gluten deja gluten en el aceite; la pasta deja gluten en el agua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>▸ Los guantes. Se cambian ANTES de tocar el plato del comensal alérgico, no después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>▸ Decir «creo que no lleva». Si no está comprobado en la matriz, la respuesta honesta es que no se puede garantizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -623,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -632,352 +830,533 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="4" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>LOS 14 ALÉRGENOS DE DECLARACIÓN OBLIGATORIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Reglamento UE 1169/2011 — Real Decreto 126/2015</t>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Reglamento (UE) 1169/2011 — Real Decreto 126/2015</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Alérgeno</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Dónde se encuentra frecuentemente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Dónde se encuentra con más frecuencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Gluten</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Cereales con gluten: trigo, centeno, cebada, avena, espelta, kamut y sus derivados</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Pan, pasta, bollería, rebozados, cerveza, salsas con harina, cuscús, seitan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Pan, pasta, bollería, rebozados, cerveza, salsas con harina, cuscús, seitán</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Crustáceos</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Cangrejos, langostinos, gambas, bogavante, nécora, cigalas y derivados</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Paella, salpicón de marisco, croquetas de marisco, sopas de pescado, surimi</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Huevos</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Huevos y derivados de cualquier ave</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Tortillas, rebozados, mayonesa, pasta fresca, merengue, bizcochos, helados, flanes</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Pescado</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Todas las especies de pescado y derivados</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Todas las especies de pescado y sus derivados</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Paella, caldos, sopas, surimi, salsa Worcestershire, gelatina de pescado</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Cacahuetes</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Cacahuetes y derivados</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Salsas asiáticas, aceite de cacahuete, mantequilla de cacahuete, snacks, postres</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Semillas de soja y derivados</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Salsa de soja, tofu, lecitina (E322), aceite de soja, miso, tempeh, edamame</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Lácteos</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Leche de vaca, cabra, oveja y derivados (incluida lactosa)</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Leche de vaca, cabra y oveja y sus derivados (incluida la lactosa)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Quesos, nata, mantequilla, yogur, bechamel, helados, chocolate con leche</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Frutos de cáscara</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Almendras, avellanas, nueces, anacardos, pecanas, pistachos, macadamias, nuez de Brasil</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Postres, pralinés, pesto, turrón, mazapán, aceites, mantequillas de frutos secos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Almendras, avellanas, nueces, anacardos, pecanas, pistachos, macadamias y nueces de Brasil</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Postres, pralinés, pesto, turrón, mazapán, aceites y mantequillas de frutos secos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Apio</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Apio y derivados (incluido sal de apio)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Sopas, caldos, ensaladas, snacks, salsas, especias mixtas</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Apio y derivados, incluida la sal de apio</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Sopas, caldos, ensaladas, snacks, salsas, mezclas de especias</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Mostaza</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Semillas de mostaza y derivados</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Salsas, vinagretas, encurtidos, marinados, especias, curry en polvo</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Sésamo</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Semillas de sésamo y derivados</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Pan de hamburguesa, hummus, tahini, aceite de sésamo, sushi, ensaladas</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Sulfitos</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Dióxido de azufre y sulfitos (&gt; 10 mg/kg o 10 mg/L)</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Dióxido de azufre y sulfitos en concentración superior a 10 mg/kg o 10 mg/L expresado como SO2</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Vino, cerveza, vinagre, frutas desecadas, crustáceos, patatas procesadas</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Altramuces</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Altramuces y derivados</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Harina de altramuz en pan/bollería, snacks, sustitutos de café</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Harina de altramuz en pan y bollería, snacks, sustitutos del café</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Moluscos</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Mejillones, almejas, ostras, calamares, pulpo, caracoles y derivados</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Paella, fideuá, tapas, ensaladas de marisco, tinta de calamar</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20">
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PROTOCOLO: Si un cliente informa de alergia → consultar carta de alérgenos → informar al chef → preparar con utensilios limpios → servir con aviso al camarero</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Imprimir y colocar en zona visible de cocina y barra. Todo el personal debe conocer estos alérgenos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>PROTOCOLO ANTE UNA ALERGIA DECLARADA — ANTES DE COCINAR Y AL SERVIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Escucha y ANOTA la alergia en la comanda con el nombre del alérgeno. Nunca la transmitas sólo de palabra.</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Consulta la matriz de alérgenos (registro 08) del plato COMPLETO: salsas, guarniciones, panes, fritos y aliños incluidos.</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Avisa al jefe de cocina antes de lanzar la comanda. El plato lo elabora UNA sola persona, de principio a fin.</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Cámbiate los guantes, lávate las manos y usa tabla, cuchillo y utensilios exclusivos en una zona de trabajo despejada.</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>No compartas freidora, aceite, agua de cocción, plancha ni tostadora sin limpiarlas antes: es la vía de contaminación más frecuente.</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Si no puedes garantizar la ausencia del alérgeno, DILO: «no podemos garantizar que este plato esté libre de …», y ofrece una alternativa. Saca el plato aparte, tapado e identificado, y entrégalo EN MANO al comensal alérgico.</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="28" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>SI UN COMENSAL EMPIEZA UNA REACCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Llama al 112 ante cualquier síntoma: dificultad para respirar, hinchazón de labios o lengua, mareo, vómitos o urticaria extensa. El 112 se llama por SÍNTOMAS, no por precaución. Es lo PRIMERO que se hace.</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Si la persona lleva adrenalina autoinyectable, ayúdala a usarla siguiendo sus indicaciones —se administra a la vez que se llama—. No la muevas ni la dejes sola.</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Deja de servir de inmediato y guarda el plato, el envase y la etiqueta del producto: harán falta para investigar qué pasó.</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>Anota el incidente el mismo día en el registro 11 (Acciones Correctivas): plato, lote, quién lo elaboró y qué se hizo.</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="28" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="12.2" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>Imprime estas fichas y cuélgalas en la cocina y en la barra. Todo el personal, de cocina y de sala, tiene que conocer los 14 alérgenos y este protocolo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24.5" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>La declaración de alérgenos de cada uno de tus platos va en el registro 08 (Matriz de alérgenos). Este cartel es la referencia y el protocolo; la matriz es el documento que se le enseña al cliente que lo pide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24.5" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="12.2" customHeight="1">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B20:D20"/>
+  <mergeCells count="18">
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B23:D23"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
+++ b/astro-site/public/dl/pack-appcc/14-fichas-14-alergenos.xlsx
@@ -1337,23 +1337,23 @@
     <row r="60"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B23:D23"/>
   </mergeCells>
   <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
